--- a/00_j24_isotopes.xlsx
+++ b/00_j24_isotopes.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC55"/>
+  <dimension ref="A1:AC57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1752,7 +1752,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="D19" t="n">
         <v>78.3035</v>
@@ -1760,53 +1760,47 @@
       <c r="E19" t="n">
         <v>-153.22</v>
       </c>
-      <c r="F19" s="1" t="n">
-        <v>45544</v>
-      </c>
-      <c r="G19" s="2" t="n">
-        <v>0.6479398148148148</v>
-      </c>
       <c r="H19" t="n">
-        <v>224.333</v>
+        <v>193.524</v>
       </c>
       <c r="I19" t="n">
-        <v>221.8519304759204</v>
+        <v>191.397933868261</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.6304</v>
+        <v>-0.8829</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.6344540475171512</v>
+        <v>-0.8846551010513305</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.6372857673286217</v>
+        <v>-0.8882592306462014</v>
       </c>
       <c r="M19" t="n">
-        <v>34.4121</v>
+        <v>34.1852</v>
       </c>
       <c r="N19" t="n">
-        <v>34.57956076043028</v>
+        <v>34.35291639883669</v>
       </c>
       <c r="O19" t="n">
-        <v>27.66775136495289</v>
+        <v>27.495782966143</v>
       </c>
       <c r="P19" t="n">
-        <v>1.027716254686474</v>
+        <v>1.027544385948226</v>
       </c>
       <c r="Q19" t="n">
-        <v>6033279332.885753</v>
+        <v>1604223377.588382</v>
       </c>
       <c r="R19" t="n">
-        <v>1874280.653207872</v>
+        <v>135579.8996843994</v>
       </c>
       <c r="S19" t="n">
-        <v>0.03106570324022098</v>
+        <v>0.00845143522894023</v>
       </c>
       <c r="T19" t="n">
-        <v>620.0499239470652</v>
+        <v>164.8410725447843</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1926228693146111</v>
+        <v>0.01393143647681282</v>
       </c>
     </row>
     <row r="20">
@@ -1821,7 +1815,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="D20" t="n">
         <v>78.3035</v>
@@ -1836,46 +1830,46 @@
         <v>0.6479398148148148</v>
       </c>
       <c r="H20" t="n">
-        <v>288.149</v>
+        <v>224.333</v>
       </c>
       <c r="I20" t="n">
-        <v>284.9181938106599</v>
+        <v>221.8519304759204</v>
       </c>
       <c r="J20" t="n">
-        <v>0.5407</v>
+        <v>-0.6304</v>
       </c>
       <c r="K20" t="n">
-        <v>0.529307539049499</v>
+        <v>-0.6344540475171512</v>
       </c>
       <c r="L20" t="n">
-        <v>0.5285629775222074</v>
+        <v>-0.6372857673286217</v>
       </c>
       <c r="M20" t="n">
-        <v>34.7131</v>
+        <v>34.4121</v>
       </c>
       <c r="N20" t="n">
-        <v>34.8805722424951</v>
+        <v>34.57956076043028</v>
       </c>
       <c r="O20" t="n">
-        <v>27.84844801650934</v>
+        <v>27.66775136495289</v>
       </c>
       <c r="P20" t="n">
-        <v>1.027896565767443</v>
+        <v>1.027716254686474</v>
       </c>
       <c r="Q20" t="n">
-        <v>4202392865.93324</v>
+        <v>6033279332.885753</v>
       </c>
       <c r="R20" t="n">
-        <v>825952.7391930108</v>
+        <v>1874280.653207872</v>
       </c>
       <c r="S20" t="n">
-        <v>0.01965434374041058</v>
+        <v>0.03106570324022098</v>
       </c>
       <c r="T20" t="n">
-        <v>431.962519489838</v>
+        <v>620.0499239470652</v>
       </c>
       <c r="U20" t="n">
-        <v>0.08489939841027085</v>
+        <v>0.1926228693146111</v>
       </c>
     </row>
     <row r="21">
@@ -1890,7 +1884,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="D21" t="n">
         <v>78.3035</v>
@@ -1905,46 +1899,46 @@
         <v>0.6479398148148148</v>
       </c>
       <c r="H21" t="n">
-        <v>458.425</v>
+        <v>288.149</v>
       </c>
       <c r="I21" t="n">
-        <v>453.0989072980764</v>
+        <v>284.9181938106599</v>
       </c>
       <c r="J21" t="n">
-        <v>0.9801</v>
+        <v>0.5407</v>
       </c>
       <c r="K21" t="n">
-        <v>0.9578766577023278</v>
+        <v>0.529307539049499</v>
       </c>
       <c r="L21" t="n">
-        <v>0.9582684704387771</v>
+        <v>0.5285629775222074</v>
       </c>
       <c r="M21" t="n">
-        <v>34.8413</v>
+        <v>34.7131</v>
       </c>
       <c r="N21" t="n">
-        <v>35.0089356875713</v>
+        <v>34.8805722424951</v>
       </c>
       <c r="O21" t="n">
-        <v>27.92389625598526</v>
+        <v>27.84844801650934</v>
       </c>
       <c r="P21" t="n">
-        <v>1.027971874167903</v>
+        <v>1.027896565767443</v>
       </c>
       <c r="Q21" t="n">
-        <v>3313318553.204499</v>
+        <v>4202392865.93324</v>
       </c>
       <c r="R21" t="n">
-        <v>580771.9903087282</v>
+        <v>825952.7391930108</v>
       </c>
       <c r="S21" t="n">
-        <v>0.01752840787816887</v>
+        <v>0.01965434374041058</v>
       </c>
       <c r="T21" t="n">
-        <v>340.5998282852913</v>
+        <v>431.962519489838</v>
       </c>
       <c r="U21" t="n">
-        <v>0.05970172713418865</v>
+        <v>0.08489939841027085</v>
       </c>
     </row>
     <row r="22">
@@ -1959,7 +1953,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="D22" t="n">
         <v>78.3035</v>
@@ -1974,46 +1968,46 @@
         <v>0.6479398148148148</v>
       </c>
       <c r="H22" t="n">
-        <v>610.567</v>
+        <v>458.425</v>
       </c>
       <c r="I22" t="n">
-        <v>603.2525459049598</v>
+        <v>453.0989072980764</v>
       </c>
       <c r="J22" t="n">
-        <v>0.8113</v>
+        <v>0.9801</v>
       </c>
       <c r="K22" t="n">
-        <v>0.7819433449614002</v>
+        <v>0.9578766577023278</v>
       </c>
       <c r="L22" t="n">
-        <v>0.7822544924738161</v>
+        <v>0.9582684704387771</v>
       </c>
       <c r="M22" t="n">
-        <v>34.8624</v>
+        <v>34.8413</v>
       </c>
       <c r="N22" t="n">
-        <v>35.02987375997005</v>
+        <v>35.0089356875713</v>
       </c>
       <c r="O22" t="n">
-        <v>27.95217938110954</v>
+        <v>27.92389625598526</v>
       </c>
       <c r="P22" t="n">
-        <v>1.028000207895902</v>
+        <v>1.027971874167903</v>
       </c>
       <c r="Q22" t="n">
-        <v>3208039729.568195</v>
+        <v>3313318553.204499</v>
       </c>
       <c r="R22" t="n">
-        <v>541017.9243001175</v>
+        <v>580771.9903087282</v>
       </c>
       <c r="S22" t="n">
-        <v>0.01686443965495836</v>
+        <v>0.01752840787816887</v>
       </c>
       <c r="T22" t="n">
-        <v>329.7865508934418</v>
+        <v>340.5998282852913</v>
       </c>
       <c r="U22" t="n">
-        <v>0.05561665386559302</v>
+        <v>0.05970172713418865</v>
       </c>
     </row>
     <row r="23">
@@ -2028,7 +2022,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="D23" t="n">
         <v>78.3035</v>
@@ -2043,46 +2037,46 @@
         <v>0.6479398148148148</v>
       </c>
       <c r="H23" t="n">
-        <v>813.385</v>
+        <v>610.567</v>
       </c>
       <c r="I23" t="n">
-        <v>803.2502487160409</v>
+        <v>603.2525459049598</v>
       </c>
       <c r="J23" t="n">
-        <v>0.4406</v>
+        <v>0.8113</v>
       </c>
       <c r="K23" t="n">
-        <v>0.4030625070284377</v>
+        <v>0.7819433449614002</v>
       </c>
       <c r="L23" t="n">
-        <v>0.402981005554696</v>
+        <v>0.7822544924738161</v>
       </c>
       <c r="M23" t="n">
-        <v>34.8713</v>
+        <v>34.8624</v>
       </c>
       <c r="N23" t="n">
-        <v>35.03864114680942</v>
+        <v>35.02987375997005</v>
       </c>
       <c r="O23" t="n">
-        <v>27.98267571092697</v>
+        <v>27.95217938110954</v>
       </c>
       <c r="P23" t="n">
-        <v>1.028030817477308</v>
+        <v>1.028000207895902</v>
       </c>
       <c r="Q23" t="n">
-        <v>3203219681.482369</v>
+        <v>3208039729.568195</v>
       </c>
       <c r="R23" t="n">
-        <v>596293.7554884844</v>
+        <v>541017.9243001175</v>
       </c>
       <c r="S23" t="n">
-        <v>0.01861544991545927</v>
+        <v>0.01686443965495836</v>
       </c>
       <c r="T23" t="n">
-        <v>329.3008547713721</v>
+        <v>329.7865508934418</v>
       </c>
       <c r="U23" t="n">
-        <v>0.06130083569114404</v>
+        <v>0.05561665386559302</v>
       </c>
     </row>
     <row r="24">
@@ -2097,7 +2091,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="D24" t="n">
         <v>78.3035</v>
@@ -2112,46 +2106,46 @@
         <v>0.6479398148148148</v>
       </c>
       <c r="H24" t="n">
-        <v>1016.524</v>
+        <v>813.385</v>
       </c>
       <c r="I24" t="n">
-        <v>1003.371276622256</v>
+        <v>803.2502487160409</v>
       </c>
       <c r="J24" t="n">
-        <v>0.1817</v>
+        <v>0.4406</v>
       </c>
       <c r="K24" t="n">
-        <v>0.1354001727755979</v>
+        <v>0.4030625070284377</v>
       </c>
       <c r="L24" t="n">
-        <v>0.1350534811152432</v>
+        <v>0.402981005554696</v>
       </c>
       <c r="M24" t="n">
-        <v>34.8817</v>
+        <v>34.8713</v>
       </c>
       <c r="N24" t="n">
-        <v>35.04905462388312</v>
+        <v>35.03864114680942</v>
       </c>
       <c r="O24" t="n">
-        <v>28.00647140978685</v>
+        <v>27.98267571092697</v>
       </c>
       <c r="P24" t="n">
-        <v>1.02805469367371</v>
+        <v>1.028030817477308</v>
       </c>
       <c r="Q24" t="n">
-        <v>3024650130.304041</v>
+        <v>3203219681.482369</v>
       </c>
       <c r="R24" t="n">
-        <v>495926.2194708871</v>
+        <v>596293.7554884844</v>
       </c>
       <c r="S24" t="n">
-        <v>0.01639615155823117</v>
+        <v>0.01861544991545927</v>
       </c>
       <c r="T24" t="n">
-        <v>310.950576317987</v>
+        <v>329.3008547713721</v>
       </c>
       <c r="U24" t="n">
-        <v>0.05098392776429041</v>
+        <v>0.06130083569114404</v>
       </c>
     </row>
     <row r="25">
@@ -2166,7 +2160,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="D25" t="n">
         <v>78.3035</v>
@@ -2181,46 +2175,46 @@
         <v>0.6479398148148148</v>
       </c>
       <c r="H25" t="n">
-        <v>1525.339</v>
+        <v>1016.524</v>
       </c>
       <c r="I25" t="n">
-        <v>1503.786198197662</v>
+        <v>1003.371276622256</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.2341</v>
+        <v>0.1817</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.3049315371919764</v>
+        <v>0.1354001727755979</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.3057179645987141</v>
+        <v>0.1350534811152432</v>
       </c>
       <c r="M25" t="n">
-        <v>34.9021</v>
+        <v>34.8817</v>
       </c>
       <c r="N25" t="n">
-        <v>35.07008250376362</v>
+        <v>35.04905462388312</v>
       </c>
       <c r="O25" t="n">
-        <v>28.04669860282843</v>
+        <v>28.00647140978685</v>
       </c>
       <c r="P25" t="n">
-        <v>1.028095054521391</v>
+        <v>1.02805469367371</v>
       </c>
       <c r="Q25" t="n">
-        <v>1603610605.571767</v>
+        <v>3024650130.304041</v>
       </c>
       <c r="R25" t="n">
-        <v>125650.8450309571</v>
+        <v>495926.2194708871</v>
       </c>
       <c r="S25" t="n">
-        <v>0.007835496010963103</v>
+        <v>0.01639615155823117</v>
       </c>
       <c r="T25" t="n">
-        <v>164.8664132966387</v>
+        <v>310.950576317987</v>
       </c>
       <c r="U25" t="n">
-        <v>0.01291810123727607</v>
+        <v>0.05098392776429041</v>
       </c>
     </row>
     <row r="26">
@@ -2235,7 +2229,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="D26" t="n">
         <v>78.3035</v>
@@ -2250,46 +2244,46 @@
         <v>0.6479398148148148</v>
       </c>
       <c r="H26" t="n">
-        <v>2033.987</v>
+        <v>1525.339</v>
       </c>
       <c r="I26" t="n">
-        <v>2002.850718520695</v>
+        <v>1503.786198197662</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.3968</v>
+        <v>-0.2341</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.497898100058437</v>
+        <v>-0.3049315371919764</v>
       </c>
       <c r="L26" t="n">
-        <v>-0.4987747987462977</v>
+        <v>-0.3057179645987141</v>
       </c>
       <c r="M26" t="n">
-        <v>34.9412</v>
+        <v>34.9021</v>
       </c>
       <c r="N26" t="n">
-        <v>35.10991084133687</v>
+        <v>35.07008250376362</v>
       </c>
       <c r="O26" t="n">
-        <v>28.08813999882568</v>
+        <v>28.04669860282843</v>
       </c>
       <c r="P26" t="n">
-        <v>1.02813655233337</v>
+        <v>1.028095054521391</v>
       </c>
       <c r="Q26" t="n">
-        <v>109165938.705472</v>
+        <v>1603610605.571767</v>
       </c>
       <c r="R26" t="n">
-        <v>624.8719638433099</v>
+        <v>125650.8450309571</v>
       </c>
       <c r="S26" t="n">
-        <v>0.0005724056159396062</v>
+        <v>0.007835496010963103</v>
       </c>
       <c r="T26" t="n">
-        <v>11.223749185288</v>
+        <v>164.8664132966387</v>
       </c>
       <c r="U26" t="n">
-        <v>6.42453706555643e-05</v>
+        <v>0.01291810123727607</v>
       </c>
     </row>
     <row r="27">
@@ -2304,7 +2298,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="D27" t="n">
         <v>78.3035</v>
@@ -2319,46 +2313,46 @@
         <v>0.6479398148148148</v>
       </c>
       <c r="H27" t="n">
-        <v>2386.327</v>
+        <v>2033.987</v>
       </c>
       <c r="I27" t="n">
-        <v>2347.86671676637</v>
+        <v>2002.850718520695</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.375</v>
+        <v>-0.3968</v>
       </c>
       <c r="K27" t="n">
-        <v>-0.5014594962504205</v>
+        <v>-0.497898100058437</v>
       </c>
       <c r="L27" t="n">
-        <v>-0.5023175449377935</v>
+        <v>-0.4987747987462977</v>
       </c>
       <c r="M27" t="n">
-        <v>34.9474</v>
+        <v>34.9412</v>
       </c>
       <c r="N27" t="n">
-        <v>35.11631078161842</v>
+        <v>35.10991084133687</v>
       </c>
       <c r="O27" t="n">
-        <v>28.09345659066253</v>
+        <v>28.08813999882568</v>
       </c>
       <c r="P27" t="n">
-        <v>1.028141869455373</v>
+        <v>1.02813655233337</v>
       </c>
       <c r="Q27" t="n">
-        <v>31812040.51608785</v>
+        <v>109165938.705472</v>
       </c>
       <c r="R27" t="n">
-        <v>65.97926154761953</v>
+        <v>624.8719638433099</v>
       </c>
       <c r="S27" t="n">
-        <v>0.0002074034248581218</v>
+        <v>0.0005724056159396062</v>
       </c>
       <c r="T27" t="n">
-        <v>3.270729080740063</v>
+        <v>11.223749185288</v>
       </c>
       <c r="U27" t="n">
-        <v>6.783604131285455e-06</v>
+        <v>6.42453706555643e-05</v>
       </c>
     </row>
     <row r="28">
@@ -2369,65 +2363,65 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>CB5</t>
+          <t>CB10</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>702</v>
+        <v>441</v>
       </c>
       <c r="D28" t="n">
-        <v>75.3035</v>
+        <v>78.3035</v>
       </c>
       <c r="E28" t="n">
-        <v>-153.289333333333</v>
+        <v>-153.22</v>
       </c>
       <c r="F28" s="1" t="n">
-        <v>45550</v>
+        <v>45544</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>0.3411226851851852</v>
+        <v>0.6479398148148148</v>
       </c>
       <c r="H28" t="n">
-        <v>6.042</v>
+        <v>2386.327</v>
       </c>
       <c r="I28" t="n">
-        <v>5.979074881416983</v>
+        <v>2347.86671676637</v>
       </c>
       <c r="J28" t="n">
-        <v>0.3993</v>
+        <v>-0.375</v>
       </c>
       <c r="K28" t="n">
-        <v>0.4361398054424697</v>
+        <v>-0.5014594962504205</v>
       </c>
       <c r="L28" t="n">
-        <v>0.3991810366191533</v>
+        <v>-0.5023175449377935</v>
       </c>
       <c r="M28" t="n">
-        <v>25.4037</v>
+        <v>34.9474</v>
       </c>
       <c r="N28" t="n">
-        <v>25.525941431768</v>
+        <v>35.11631078161842</v>
       </c>
       <c r="O28" t="n">
-        <v>20.36110632882423</v>
+        <v>28.09345659066253</v>
       </c>
       <c r="P28" t="n">
-        <v>1.020410094592409</v>
+        <v>1.028141869455373</v>
       </c>
       <c r="Q28" t="n">
-        <v>157838998.5610546</v>
+        <v>31812040.51608785</v>
       </c>
       <c r="R28" t="n">
-        <v>1367.904342430322</v>
+        <v>65.97926154761953</v>
       </c>
       <c r="S28" t="n">
-        <v>0.0008666453505793091</v>
+        <v>0.0002074034248581218</v>
       </c>
       <c r="T28" t="n">
-        <v>16.10605074520568</v>
+        <v>3.270729080740063</v>
       </c>
       <c r="U28" t="n">
-        <v>0.0001395823399452692</v>
+        <v>6.783604131285455e-06</v>
       </c>
     </row>
     <row r="29">
@@ -2442,13 +2436,13 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>699</v>
+        <v>702</v>
       </c>
       <c r="D29" t="n">
         <v>75.3035</v>
       </c>
       <c r="E29" t="n">
-        <v>-153.2893333333333</v>
+        <v>-153.289333333333</v>
       </c>
       <c r="F29" s="1" t="n">
         <v>45550</v>
@@ -2457,46 +2451,46 @@
         <v>0.3411226851851852</v>
       </c>
       <c r="H29" t="n">
-        <v>58.344</v>
+        <v>6.042</v>
       </c>
       <c r="I29" t="n">
-        <v>57.72904209073982</v>
+        <v>5.979074881416983</v>
       </c>
       <c r="J29" t="n">
-        <v>0.1443</v>
+        <v>0.3993</v>
       </c>
       <c r="K29" t="n">
-        <v>0.1579380800959715</v>
+        <v>0.4361398054424697</v>
       </c>
       <c r="L29" t="n">
-        <v>0.142560195683067</v>
+        <v>0.3991810366191533</v>
       </c>
       <c r="M29" t="n">
-        <v>31.2814</v>
+        <v>25.4037</v>
       </c>
       <c r="N29" t="n">
-        <v>31.43269814972568</v>
+        <v>25.525941431768</v>
       </c>
       <c r="O29" t="n">
-        <v>25.10469518402897</v>
+        <v>20.36110632882423</v>
       </c>
       <c r="P29" t="n">
-        <v>1.025153236424765</v>
+        <v>1.020410094592409</v>
       </c>
       <c r="Q29" t="n">
-        <v>121366075.3009852</v>
+        <v>157838998.5610546</v>
       </c>
       <c r="R29" t="n">
-        <v>745.6633641188877</v>
+        <v>1367.904342430322</v>
       </c>
       <c r="S29" t="n">
-        <v>0.0006143919231710005</v>
+        <v>0.0008666453505793091</v>
       </c>
       <c r="T29" t="n">
-        <v>12.44188248869767</v>
+        <v>16.10605074520568</v>
       </c>
       <c r="U29" t="n">
-        <v>7.644192110098555e-05</v>
+        <v>0.0001395823399452692</v>
       </c>
     </row>
     <row r="30">
@@ -2511,7 +2505,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="D30" t="n">
         <v>75.3035</v>
@@ -2526,46 +2520,46 @@
         <v>0.3411226851851852</v>
       </c>
       <c r="H30" t="n">
-        <v>78.84699999999999</v>
+        <v>58.344</v>
       </c>
       <c r="I30" t="n">
-        <v>78.01205722796831</v>
+        <v>57.72904209073982</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.7063</v>
+        <v>0.1443</v>
       </c>
       <c r="K30" t="n">
-        <v>-0.6979357512655953</v>
+        <v>0.1579380800959715</v>
       </c>
       <c r="L30" t="n">
-        <v>-0.7081554588831565</v>
+        <v>0.142560195683067</v>
       </c>
       <c r="M30" t="n">
-        <v>31.8782</v>
+        <v>31.2814</v>
       </c>
       <c r="N30" t="n">
-        <v>32.0330023973173</v>
+        <v>31.43269814972568</v>
       </c>
       <c r="O30" t="n">
-        <v>25.6210953789589</v>
+        <v>25.10469518402897</v>
       </c>
       <c r="P30" t="n">
-        <v>1.025669851032883</v>
+        <v>1.025153236424765</v>
       </c>
       <c r="Q30" t="n">
-        <v>91268458.648718</v>
+        <v>121366075.3009852</v>
       </c>
       <c r="R30" t="n">
-        <v>464.6439685875562</v>
+        <v>745.6633641188877</v>
       </c>
       <c r="S30" t="n">
-        <v>0.0005090958864287588</v>
+        <v>0.0006143919231710005</v>
       </c>
       <c r="T30" t="n">
-        <v>9.361130638623139</v>
+        <v>12.44188248869767</v>
       </c>
       <c r="U30" t="n">
-        <v>4.765713100445261e-05</v>
+        <v>7.644192110098555e-05</v>
       </c>
     </row>
     <row r="31">
@@ -2580,7 +2574,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>694</v>
+        <v>698</v>
       </c>
       <c r="D31" t="n">
         <v>75.3035</v>
@@ -2595,46 +2589,46 @@
         <v>0.3411226851851852</v>
       </c>
       <c r="H31" t="n">
-        <v>199.666</v>
+        <v>78.84699999999999</v>
       </c>
       <c r="I31" t="n">
-        <v>197.4938567099203</v>
+        <v>78.01205722796831</v>
       </c>
       <c r="J31" t="n">
-        <v>-1.4541</v>
+        <v>-0.7063</v>
       </c>
       <c r="K31" t="n">
-        <v>-1.452506361968724</v>
+        <v>-0.6979357512655953</v>
       </c>
       <c r="L31" t="n">
-        <v>-1.458176236545848</v>
+        <v>-0.7081554588831565</v>
       </c>
       <c r="M31" t="n">
-        <v>33.118</v>
+        <v>31.8782</v>
       </c>
       <c r="N31" t="n">
-        <v>33.27987159636913</v>
+        <v>32.0330023973173</v>
       </c>
       <c r="O31" t="n">
-        <v>26.64995263451965</v>
+        <v>25.6210953789589</v>
       </c>
       <c r="P31" t="n">
-        <v>1.026698836412697</v>
+        <v>1.025669851032883</v>
       </c>
       <c r="Q31" t="n">
-        <v>319593708.6144769</v>
+        <v>91268458.648718</v>
       </c>
       <c r="R31" t="n">
-        <v>5147.027082493969</v>
+        <v>464.6439685875562</v>
       </c>
       <c r="S31" t="n">
-        <v>0.001610490739885866</v>
+        <v>0.0005090958864287588</v>
       </c>
       <c r="T31" t="n">
-        <v>32.81264887593019</v>
+        <v>9.361130638623139</v>
       </c>
       <c r="U31" t="n">
-        <v>0.0005284446716581196</v>
+        <v>4.765713100445261e-05</v>
       </c>
     </row>
     <row r="32">
@@ -2649,7 +2643,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="D32" t="n">
         <v>75.3035</v>
@@ -2664,46 +2658,46 @@
         <v>0.3411226851851852</v>
       </c>
       <c r="H32" t="n">
-        <v>229.51</v>
+        <v>199.666</v>
       </c>
       <c r="I32" t="n">
-        <v>226.9968014614902</v>
+        <v>197.4938567099203</v>
       </c>
       <c r="J32" t="n">
-        <v>-1.0989</v>
+        <v>-1.4541</v>
       </c>
       <c r="K32" t="n">
-        <v>-1.099830146051212</v>
+        <v>-1.452506361968724</v>
       </c>
       <c r="L32" t="n">
-        <v>-1.104666391127369</v>
+        <v>-1.458176236545848</v>
       </c>
       <c r="M32" t="n">
-        <v>33.7016</v>
+        <v>33.118</v>
       </c>
       <c r="N32" t="n">
-        <v>33.86551180762911</v>
+        <v>33.27987159636913</v>
       </c>
       <c r="O32" t="n">
-        <v>27.11112820413041</v>
+        <v>26.64995263451965</v>
       </c>
       <c r="P32" t="n">
-        <v>1.027159844384232</v>
+        <v>1.026698836412697</v>
       </c>
       <c r="Q32" t="n">
-        <v>1024019810.634743</v>
+        <v>319593708.6144769</v>
       </c>
       <c r="R32" t="n">
-        <v>55133.94885470799</v>
+        <v>5147.027082493969</v>
       </c>
       <c r="S32" t="n">
-        <v>0.00538407053087508</v>
+        <v>0.001610490739885866</v>
       </c>
       <c r="T32" t="n">
-        <v>105.1832029337953</v>
+        <v>32.81264887593019</v>
       </c>
       <c r="U32" t="n">
-        <v>0.005663137832589008</v>
+        <v>0.0005284446716581196</v>
       </c>
     </row>
     <row r="33">
@@ -2718,7 +2712,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="D33" t="n">
         <v>75.3035</v>
@@ -2733,46 +2727,46 @@
         <v>0.3411226851851852</v>
       </c>
       <c r="H33" t="n">
-        <v>253.484</v>
+        <v>229.51</v>
       </c>
       <c r="I33" t="n">
-        <v>250.6937496465414</v>
+        <v>226.9968014614902</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.6032999999999999</v>
+        <v>-1.0989</v>
       </c>
       <c r="K33" t="n">
-        <v>-0.6074841015682626</v>
+        <v>-1.099830146051212</v>
       </c>
       <c r="L33" t="n">
-        <v>-0.6110930709823165</v>
+        <v>-1.104666391127369</v>
       </c>
       <c r="M33" t="n">
-        <v>34.1749</v>
+        <v>33.7016</v>
       </c>
       <c r="N33" t="n">
-        <v>34.34056747598297</v>
+        <v>33.86551180762911</v>
       </c>
       <c r="O33" t="n">
-        <v>27.47427427596858</v>
+        <v>27.11112820413041</v>
       </c>
       <c r="P33" t="n">
-        <v>1.027522790880821</v>
+        <v>1.027159844384232</v>
       </c>
       <c r="Q33" t="n">
-        <v>1845518437.274079</v>
+        <v>1024019810.634743</v>
       </c>
       <c r="R33" t="n">
-        <v>192028.8891119289</v>
+        <v>55133.94885470799</v>
       </c>
       <c r="S33" t="n">
-        <v>0.01040514606809157</v>
+        <v>0.00538407053087508</v>
       </c>
       <c r="T33" t="n">
-        <v>189.6312255289873</v>
+        <v>105.1832029337953</v>
       </c>
       <c r="U33" t="n">
-        <v>0.01973140600700329</v>
+        <v>0.005663137832589008</v>
       </c>
     </row>
     <row r="34">
@@ -2787,7 +2781,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="D34" t="n">
         <v>75.3035</v>
@@ -2802,46 +2796,46 @@
         <v>0.3411226851851852</v>
       </c>
       <c r="H34" t="n">
-        <v>276.668</v>
+        <v>253.484</v>
       </c>
       <c r="I34" t="n">
-        <v>273.6072207360575</v>
+        <v>250.6937496465414</v>
       </c>
       <c r="J34" t="n">
-        <v>-0.2927</v>
+        <v>-0.6032999999999999</v>
       </c>
       <c r="K34" t="n">
-        <v>-0.2994156332787914</v>
+        <v>-0.6074841015682626</v>
       </c>
       <c r="L34" t="n">
-        <v>-0.3021478112560833</v>
+        <v>-0.6110930709823165</v>
       </c>
       <c r="M34" t="n">
-        <v>34.3972</v>
+        <v>34.1749</v>
       </c>
       <c r="N34" t="n">
-        <v>34.56365160375395</v>
+        <v>34.34056747598297</v>
       </c>
       <c r="O34" t="n">
-        <v>27.63945162616096</v>
+        <v>27.47427427596858</v>
       </c>
       <c r="P34" t="n">
-        <v>1.027687851705269</v>
+        <v>1.027522790880821</v>
       </c>
       <c r="Q34" t="n">
-        <v>2286685931.357832</v>
+        <v>1845518437.274079</v>
       </c>
       <c r="R34" t="n">
-        <v>279835.6047297722</v>
+        <v>192028.8891119289</v>
       </c>
       <c r="S34" t="n">
-        <v>0.01223760556236973</v>
+        <v>0.01040514606809157</v>
       </c>
       <c r="T34" t="n">
-        <v>234.9999352321793</v>
+        <v>189.6312255289873</v>
       </c>
       <c r="U34" t="n">
-        <v>0.02875836514553844</v>
+        <v>0.01973140600700329</v>
       </c>
     </row>
     <row r="35">
@@ -2856,7 +2850,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="D35" t="n">
         <v>75.3035</v>
@@ -2871,46 +2865,46 @@
         <v>0.3411226851851852</v>
       </c>
       <c r="H35" t="n">
-        <v>353.192</v>
+        <v>276.668</v>
       </c>
       <c r="I35" t="n">
-        <v>349.2201113107141</v>
+        <v>273.6072207360575</v>
       </c>
       <c r="J35" t="n">
-        <v>0.4422</v>
+        <v>-0.2927</v>
       </c>
       <c r="K35" t="n">
-        <v>0.4282189967745359</v>
+        <v>-0.2994156332787914</v>
       </c>
       <c r="L35" t="n">
-        <v>0.4274115573699181</v>
+        <v>-0.3021478112560833</v>
       </c>
       <c r="M35" t="n">
-        <v>34.7192</v>
+        <v>34.3972</v>
       </c>
       <c r="N35" t="n">
-        <v>34.88687560705182</v>
+        <v>34.56365160375395</v>
       </c>
       <c r="O35" t="n">
-        <v>27.85956217872445</v>
+        <v>27.63945162616096</v>
       </c>
       <c r="P35" t="n">
-        <v>1.027907709926541</v>
+        <v>1.027687851705269</v>
       </c>
       <c r="Q35" t="n">
-        <v>2442951170.626579</v>
+        <v>2286685931.357832</v>
       </c>
       <c r="R35" t="n">
-        <v>313834.0477664113</v>
+        <v>279835.6047297722</v>
       </c>
       <c r="S35" t="n">
-        <v>0.01284651332944644</v>
+        <v>0.01223760556236973</v>
       </c>
       <c r="T35" t="n">
-        <v>251.1128343261129</v>
+        <v>234.9999352321793</v>
       </c>
       <c r="U35" t="n">
-        <v>0.03225924373365486</v>
+        <v>0.02875836514553844</v>
       </c>
     </row>
     <row r="36">
@@ -2925,7 +2919,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="D36" t="n">
         <v>75.3035</v>
@@ -2940,46 +2934,46 @@
         <v>0.3411226851851852</v>
       </c>
       <c r="H36" t="n">
-        <v>505.081</v>
+        <v>353.192</v>
       </c>
       <c r="I36" t="n">
-        <v>499.2182965953946</v>
+        <v>349.2201113107141</v>
       </c>
       <c r="J36" t="n">
-        <v>0.8403</v>
+        <v>0.4422</v>
       </c>
       <c r="K36" t="n">
-        <v>0.8164084220766308</v>
+        <v>0.4282189967745359</v>
       </c>
       <c r="L36" t="n">
-        <v>0.8166375481739556</v>
+        <v>0.4274115573699181</v>
       </c>
       <c r="M36" t="n">
-        <v>34.8402</v>
+        <v>34.7192</v>
       </c>
       <c r="N36" t="n">
-        <v>35.00803069874979</v>
+        <v>34.88687560705182</v>
       </c>
       <c r="O36" t="n">
-        <v>27.93247371854113</v>
+        <v>27.85956217872445</v>
       </c>
       <c r="P36" t="n">
-        <v>1.027980493877211</v>
+        <v>1.027907709926541</v>
       </c>
       <c r="Q36" t="n">
-        <v>2177807280.446036</v>
+        <v>2442951170.626579</v>
       </c>
       <c r="R36" t="n">
-        <v>213897.2392991068</v>
+        <v>313834.0477664113</v>
       </c>
       <c r="S36" t="n">
-        <v>0.009821678952937406</v>
+        <v>0.01284651332944644</v>
       </c>
       <c r="T36" t="n">
-        <v>223.8743403722301</v>
+        <v>251.1128343261129</v>
       </c>
       <c r="U36" t="n">
-        <v>0.02198821896936678</v>
+        <v>0.03225924373365486</v>
       </c>
     </row>
     <row r="37">
@@ -2994,7 +2988,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="D37" t="n">
         <v>75.3035</v>
@@ -3009,46 +3003,46 @@
         <v>0.3411226851851852</v>
       </c>
       <c r="H37" t="n">
-        <v>610.306</v>
+        <v>505.081</v>
       </c>
       <c r="I37" t="n">
-        <v>603.0693527302871</v>
+        <v>499.2182965953946</v>
       </c>
       <c r="J37" t="n">
-        <v>0.7116</v>
+        <v>0.8403</v>
       </c>
       <c r="K37" t="n">
-        <v>0.6829330064294755</v>
+        <v>0.8164084220766308</v>
       </c>
       <c r="L37" t="n">
-        <v>0.6830901515758636</v>
+        <v>0.8166375481739556</v>
       </c>
       <c r="M37" t="n">
-        <v>34.8548</v>
+        <v>34.8402</v>
       </c>
       <c r="N37" t="n">
-        <v>35.0223731314445</v>
+        <v>35.00803069874979</v>
       </c>
       <c r="O37" t="n">
-        <v>27.95249067889358</v>
+        <v>27.93247371854113</v>
       </c>
       <c r="P37" t="n">
-        <v>1.028000549524509</v>
+        <v>1.027980493877211</v>
       </c>
       <c r="Q37" t="n">
-        <v>1979381202.237706</v>
+        <v>2177807280.446036</v>
       </c>
       <c r="R37" t="n">
-        <v>195889.6417423994</v>
+        <v>213897.2392991068</v>
       </c>
       <c r="S37" t="n">
-        <v>0.00989650914745197</v>
+        <v>0.009821678952937406</v>
       </c>
       <c r="T37" t="n">
-        <v>203.4804963618845</v>
+        <v>223.8743403722301</v>
       </c>
       <c r="U37" t="n">
-        <v>0.02013746593573457</v>
+        <v>0.02198821896936678</v>
       </c>
     </row>
     <row r="38">
@@ -3063,7 +3057,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="D38" t="n">
         <v>75.3035</v>
@@ -3078,46 +3072,46 @@
         <v>0.3411226851851852</v>
       </c>
       <c r="H38" t="n">
-        <v>813.287</v>
+        <v>610.306</v>
       </c>
       <c r="I38" t="n">
-        <v>803.2526219636235</v>
+        <v>603.0693527302871</v>
       </c>
       <c r="J38" t="n">
-        <v>0.3623</v>
+        <v>0.7116</v>
       </c>
       <c r="K38" t="n">
-        <v>0.3254257508993602</v>
+        <v>0.6829330064294755</v>
       </c>
       <c r="L38" t="n">
-        <v>0.3252304163021357</v>
+        <v>0.6830901515758636</v>
       </c>
       <c r="M38" t="n">
-        <v>34.8664</v>
+        <v>34.8548</v>
       </c>
       <c r="N38" t="n">
-        <v>35.03384754550044</v>
+        <v>35.0223731314445</v>
       </c>
       <c r="O38" t="n">
-        <v>27.98341000000801</v>
+        <v>27.95249067889358</v>
       </c>
       <c r="P38" t="n">
-        <v>1.028031575741956</v>
+        <v>1.028000549524509</v>
       </c>
       <c r="Q38" t="n">
-        <v>1859643622.927298</v>
+        <v>1979381202.237706</v>
       </c>
       <c r="R38" t="n">
-        <v>192341.9694151905</v>
+        <v>195889.6417423994</v>
       </c>
       <c r="S38" t="n">
-        <v>0.01034294781235674</v>
+        <v>0.00989650914745197</v>
       </c>
       <c r="T38" t="n">
-        <v>191.177236399643</v>
+        <v>203.4804963618845</v>
       </c>
       <c r="U38" t="n">
-        <v>0.01977336178992095</v>
+        <v>0.02013746593573457</v>
       </c>
     </row>
     <row r="39">
@@ -3132,7 +3126,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="D39" t="n">
         <v>75.3035</v>
@@ -3147,46 +3141,46 @@
         <v>0.3411226851851852</v>
       </c>
       <c r="H39" t="n">
-        <v>1016.456</v>
+        <v>813.287</v>
       </c>
       <c r="I39" t="n">
-        <v>1003.427942540416</v>
+        <v>803.2526219636235</v>
       </c>
       <c r="J39" t="n">
-        <v>0.098</v>
+        <v>0.3623</v>
       </c>
       <c r="K39" t="n">
-        <v>0.05257111119056274</v>
+        <v>0.3254257508993602</v>
       </c>
       <c r="L39" t="n">
-        <v>0.05208853853243</v>
+        <v>0.3252304163021357</v>
       </c>
       <c r="M39" t="n">
-        <v>34.8731</v>
+        <v>34.8664</v>
       </c>
       <c r="N39" t="n">
-        <v>35.04054975127265</v>
+        <v>35.03384754550044</v>
       </c>
       <c r="O39" t="n">
-        <v>28.00423353430301</v>
+        <v>27.98341000000801</v>
       </c>
       <c r="P39" t="n">
-        <v>1.02805248191156</v>
+        <v>1.028031575741956</v>
       </c>
       <c r="Q39" t="n">
-        <v>1625715347.583458</v>
+        <v>1859643622.927298</v>
       </c>
       <c r="R39" t="n">
-        <v>121731.4182087444</v>
+        <v>192341.9694151905</v>
       </c>
       <c r="S39" t="n">
-        <v>0.007487867933933937</v>
+        <v>0.01034294781235674</v>
       </c>
       <c r="T39" t="n">
-        <v>167.1320697964889</v>
+        <v>191.177236399643</v>
       </c>
       <c r="U39" t="n">
-        <v>0.01251462866161138</v>
+        <v>0.01977336178992095</v>
       </c>
     </row>
     <row r="40">
@@ -3201,7 +3195,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="D40" t="n">
         <v>75.3035</v>
@@ -3216,46 +3210,46 @@
         <v>0.3411226851851852</v>
       </c>
       <c r="H40" t="n">
-        <v>1524.899</v>
+        <v>1016.456</v>
       </c>
       <c r="I40" t="n">
-        <v>1503.539204820686</v>
+        <v>1003.427942540416</v>
       </c>
       <c r="J40" t="n">
-        <v>-0.2658</v>
+        <v>0.098</v>
       </c>
       <c r="K40" t="n">
-        <v>-0.3361684842190544</v>
+        <v>0.05257111119056274</v>
       </c>
       <c r="L40" t="n">
-        <v>-0.3369914770802701</v>
+        <v>0.05208853853243</v>
       </c>
       <c r="M40" t="n">
-        <v>34.9023</v>
+        <v>34.8731</v>
       </c>
       <c r="N40" t="n">
-        <v>35.07045157153737</v>
+        <v>35.04054975127265</v>
       </c>
       <c r="O40" t="n">
-        <v>28.04855274630609</v>
+        <v>28.00423353430301</v>
       </c>
       <c r="P40" t="n">
-        <v>1.028096918323162</v>
+        <v>1.02805248191156</v>
       </c>
       <c r="Q40" t="n">
-        <v>961051632.6955394</v>
+        <v>1625715347.583458</v>
       </c>
       <c r="R40" t="n">
-        <v>51796.72863507224</v>
+        <v>121731.4182087444</v>
       </c>
       <c r="S40" t="n">
-        <v>0.005389588537485104</v>
+        <v>0.007487867933933937</v>
       </c>
       <c r="T40" t="n">
-        <v>98.80542219237277</v>
+        <v>167.1320697964889</v>
       </c>
       <c r="U40" t="n">
-        <v>0.005325205708893886</v>
+        <v>0.01251462866161138</v>
       </c>
     </row>
     <row r="41">
@@ -3270,7 +3264,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="D41" t="n">
         <v>75.3035</v>
@@ -3285,46 +3279,46 @@
         <v>0.3411226851851852</v>
       </c>
       <c r="H41" t="n">
-        <v>2034.275</v>
+        <v>1524.899</v>
       </c>
       <c r="I41" t="n">
-        <v>2003.379750617243</v>
+        <v>1503.539204820686</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.394</v>
+        <v>-0.2658</v>
       </c>
       <c r="K41" t="n">
-        <v>-0.4951185050467125</v>
+        <v>-0.3361684842190544</v>
       </c>
       <c r="L41" t="n">
-        <v>-0.4960160333229986</v>
+        <v>-0.3369914770802701</v>
       </c>
       <c r="M41" t="n">
-        <v>34.9345</v>
+        <v>34.9023</v>
       </c>
       <c r="N41" t="n">
-        <v>35.1031990886042</v>
+        <v>35.07045157153737</v>
       </c>
       <c r="O41" t="n">
-        <v>28.0826098191551</v>
+        <v>28.04855274630609</v>
       </c>
       <c r="P41" t="n">
-        <v>1.028131021895875</v>
+        <v>1.028096918323162</v>
       </c>
       <c r="Q41" t="n">
-        <v>107615750.6324065</v>
+        <v>961051632.6955394</v>
       </c>
       <c r="R41" t="n">
-        <v>643.3034650965963</v>
+        <v>51796.72863507224</v>
       </c>
       <c r="S41" t="n">
-        <v>0.0005977781703107659</v>
+        <v>0.005389588537485104</v>
       </c>
       <c r="T41" t="n">
-        <v>11.06430916697878</v>
+        <v>98.80542219237277</v>
       </c>
       <c r="U41" t="n">
-        <v>6.614002489589208e-05</v>
+        <v>0.005325205708893886</v>
       </c>
     </row>
     <row r="42">
@@ -3339,7 +3333,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="D42" t="n">
         <v>75.3035</v>
@@ -3354,46 +3348,46 @@
         <v>0.3411226851851852</v>
       </c>
       <c r="H42" t="n">
-        <v>3817.091</v>
+        <v>2034.275</v>
       </c>
       <c r="I42" t="n">
-        <v>3743.719935843988</v>
+        <v>2003.379750617243</v>
       </c>
       <c r="J42" t="n">
-        <v>-0.2524</v>
+        <v>-0.394</v>
       </c>
       <c r="K42" t="n">
-        <v>-0.5038493182456802</v>
+        <v>-0.4951185050467125</v>
       </c>
       <c r="L42" t="n">
-        <v>-0.5046854487637611</v>
+        <v>-0.4960160333229986</v>
       </c>
       <c r="M42" t="n">
-        <v>34.9538</v>
+        <v>34.9345</v>
       </c>
       <c r="N42" t="n">
-        <v>35.12321064584834</v>
+        <v>35.1031990886042</v>
       </c>
       <c r="O42" t="n">
-        <v>28.09911955266398</v>
+        <v>28.0826098191551</v>
       </c>
       <c r="P42" t="n">
-        <v>1.028147532536548</v>
+        <v>1.028131021895875</v>
       </c>
       <c r="Q42" t="n">
-        <v>785737.3786944234</v>
+        <v>107615750.6324065</v>
       </c>
       <c r="R42" t="n">
-        <v>0.1649723617230003</v>
+        <v>643.3034650965963</v>
       </c>
       <c r="S42" t="n">
-        <v>2.099586531025384e-05</v>
+        <v>0.0005977781703107659</v>
       </c>
       <c r="T42" t="n">
-        <v>0.08078539471264064</v>
+        <v>11.06430916697878</v>
       </c>
       <c r="U42" t="n">
-        <v>1.696159266422295e-08</v>
+        <v>6.614002489589208e-05</v>
       </c>
     </row>
     <row r="43">
@@ -3404,65 +3398,65 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Stn A</t>
+          <t>CB5</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>905</v>
+        <v>679</v>
       </c>
       <c r="D43" t="n">
-        <v>72.60066666666667</v>
+        <v>75.3035</v>
       </c>
       <c r="E43" t="n">
-        <v>-144.697</v>
+        <v>-153.2893333333333</v>
       </c>
       <c r="F43" s="1" t="n">
-        <v>45553</v>
+        <v>45550</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>0.5347685185185185</v>
+        <v>0.3411226851851852</v>
       </c>
       <c r="H43" t="n">
-        <v>5.502</v>
+        <v>3817.091</v>
       </c>
       <c r="I43" t="n">
-        <v>5.445428460253375</v>
+        <v>3743.719935843988</v>
       </c>
       <c r="J43" t="n">
-        <v>2.3719</v>
+        <v>-0.2524</v>
       </c>
       <c r="K43" t="n">
-        <v>2.435922143950712</v>
+        <v>-0.5038493182456802</v>
       </c>
       <c r="L43" t="n">
-        <v>2.371695542275033</v>
+        <v>-0.5046854487637611</v>
       </c>
       <c r="M43" t="n">
-        <v>25.1906</v>
+        <v>34.9538</v>
       </c>
       <c r="N43" t="n">
-        <v>25.3115093233509</v>
+        <v>35.12321064584834</v>
       </c>
       <c r="O43" t="n">
-        <v>20.10422300231198</v>
+        <v>28.09911955266398</v>
       </c>
       <c r="P43" t="n">
-        <v>1.020152620652608</v>
+        <v>1.028147532536548</v>
       </c>
       <c r="Q43" t="n">
-        <v>156163124.7758991</v>
+        <v>785737.3786944234</v>
       </c>
       <c r="R43" t="n">
-        <v>1326.754472921331</v>
+        <v>0.1649723617230003</v>
       </c>
       <c r="S43" t="n">
-        <v>0.0008495952388409755</v>
+        <v>2.099586531025384e-05</v>
       </c>
       <c r="T43" t="n">
-        <v>15.93102209894337</v>
+        <v>0.08078539471264064</v>
       </c>
       <c r="U43" t="n">
-        <v>0.0001353492052513265</v>
+        <v>1.696159266422295e-08</v>
       </c>
     </row>
     <row r="44">
@@ -3477,7 +3471,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>901</v>
+        <v>905</v>
       </c>
       <c r="D44" t="n">
         <v>72.60066666666667</v>
@@ -3492,46 +3486,46 @@
         <v>0.5347685185185185</v>
       </c>
       <c r="H44" t="n">
-        <v>94.804</v>
+        <v>5.502</v>
       </c>
       <c r="I44" t="n">
-        <v>93.80890084709274</v>
+        <v>5.445428460253375</v>
       </c>
       <c r="J44" t="n">
-        <v>-0.5432</v>
+        <v>2.3719</v>
       </c>
       <c r="K44" t="n">
-        <v>-0.5347807663268443</v>
+        <v>2.435922143950712</v>
       </c>
       <c r="L44" t="n">
-        <v>-0.54558419795498</v>
+        <v>2.371695542275033</v>
       </c>
       <c r="M44" t="n">
-        <v>31.8675</v>
+        <v>25.1906</v>
       </c>
       <c r="N44" t="n">
-        <v>32.02166754024961</v>
+        <v>25.3115093233509</v>
       </c>
       <c r="O44" t="n">
-        <v>25.60608783737143</v>
+        <v>20.10422300231198</v>
       </c>
       <c r="P44" t="n">
-        <v>1.025654792729273</v>
+        <v>1.020152620652608</v>
       </c>
       <c r="Q44" t="n">
-        <v>80540652.24182494</v>
+        <v>156163124.7758991</v>
       </c>
       <c r="R44" t="n">
-        <v>392.8290859029788</v>
+        <v>1326.754472921331</v>
       </c>
       <c r="S44" t="n">
-        <v>0.0004877401349116239</v>
+        <v>0.0008495952388409755</v>
       </c>
       <c r="T44" t="n">
-        <v>8.260690598136943</v>
+        <v>15.93102209894337</v>
       </c>
       <c r="U44" t="n">
-        <v>4.029070346798496e-05</v>
+        <v>0.0001353492052513265</v>
       </c>
     </row>
     <row r="45">
@@ -3546,7 +3540,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="D45" t="n">
         <v>72.60066666666667</v>
@@ -3561,46 +3555,46 @@
         <v>0.5347685185185185</v>
       </c>
       <c r="H45" t="n">
-        <v>129.081</v>
+        <v>94.804</v>
       </c>
       <c r="I45" t="n">
-        <v>127.7155078466131</v>
+        <v>93.80890084709274</v>
       </c>
       <c r="J45" t="n">
-        <v>-1.1654</v>
+        <v>-0.5432</v>
       </c>
       <c r="K45" t="n">
-        <v>-1.160226095417628</v>
+        <v>-0.5347807663268443</v>
       </c>
       <c r="L45" t="n">
-        <v>-1.16806874273273</v>
+        <v>-0.54558419795498</v>
       </c>
       <c r="M45" t="n">
-        <v>32.2915</v>
+        <v>31.8675</v>
       </c>
       <c r="N45" t="n">
-        <v>32.44966758020607</v>
+        <v>32.02166754024961</v>
       </c>
       <c r="O45" t="n">
-        <v>25.97169497731807</v>
+        <v>25.60608783737143</v>
       </c>
       <c r="P45" t="n">
-        <v>1.026020560611761</v>
+        <v>1.025654792729273</v>
       </c>
       <c r="Q45" t="n">
-        <v>92721980.08775106</v>
+        <v>80540652.24182494</v>
       </c>
       <c r="R45" t="n">
-        <v>454.9743070916026</v>
+        <v>392.8290859029788</v>
       </c>
       <c r="S45" t="n">
-        <v>0.0004906865736269005</v>
+        <v>0.0004877401349116239</v>
       </c>
       <c r="T45" t="n">
-        <v>9.51346579906669</v>
+        <v>8.260690598136943</v>
       </c>
       <c r="U45" t="n">
-        <v>4.668129936260737e-05</v>
+        <v>4.029070346798496e-05</v>
       </c>
     </row>
     <row r="46">
@@ -3615,7 +3609,7 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>897</v>
+        <v>900</v>
       </c>
       <c r="D46" t="n">
         <v>72.60066666666667</v>
@@ -3630,46 +3624,46 @@
         <v>0.5347685185185185</v>
       </c>
       <c r="H46" t="n">
-        <v>207.593</v>
+        <v>129.081</v>
       </c>
       <c r="I46" t="n">
-        <v>205.357930291889</v>
+        <v>127.7155078466131</v>
       </c>
       <c r="J46" t="n">
-        <v>-1.4266</v>
+        <v>-1.1654</v>
       </c>
       <c r="K46" t="n">
-        <v>-1.425126455819729</v>
+        <v>-1.160226095417628</v>
       </c>
       <c r="L46" t="n">
-        <v>-1.430893726737527</v>
+        <v>-1.16806874273273</v>
       </c>
       <c r="M46" t="n">
-        <v>33.088</v>
+        <v>32.2915</v>
       </c>
       <c r="N46" t="n">
-        <v>33.24868375950396</v>
+        <v>32.44966758020607</v>
       </c>
       <c r="O46" t="n">
-        <v>26.62399668881312</v>
+        <v>25.97169497731807</v>
       </c>
       <c r="P46" t="n">
-        <v>1.026672874456598</v>
+        <v>1.026020560611761</v>
       </c>
       <c r="Q46" t="n">
-        <v>282697279.5114288</v>
+        <v>92721980.08775106</v>
       </c>
       <c r="R46" t="n">
-        <v>4626.440395699151</v>
+        <v>454.9743070916026</v>
       </c>
       <c r="S46" t="n">
-        <v>0.001636535167121095</v>
+        <v>0.0004906865736269005</v>
       </c>
       <c r="T46" t="n">
-        <v>29.02376285570589</v>
+        <v>9.51346579906669</v>
       </c>
       <c r="U46" t="n">
-        <v>0.0004749840859554567</v>
+        <v>4.668129936260737e-05</v>
       </c>
     </row>
     <row r="47">
@@ -3684,7 +3678,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="D47" t="n">
         <v>72.60066666666667</v>
@@ -3699,46 +3693,46 @@
         <v>0.5347685185185185</v>
       </c>
       <c r="H47" t="n">
-        <v>238.694</v>
+        <v>207.593</v>
       </c>
       <c r="I47" t="n">
-        <v>236.1063197972578</v>
+        <v>205.357930291889</v>
       </c>
       <c r="J47" t="n">
-        <v>-1.0558</v>
+        <v>-1.4266</v>
       </c>
       <c r="K47" t="n">
-        <v>-1.056958930295232</v>
+        <v>-1.425126455819729</v>
       </c>
       <c r="L47" t="n">
-        <v>-1.06189709177131</v>
+        <v>-1.430893726737527</v>
       </c>
       <c r="M47" t="n">
-        <v>33.672</v>
+        <v>33.088</v>
       </c>
       <c r="N47" t="n">
-        <v>33.83515912793373</v>
+        <v>33.24868375950396</v>
       </c>
       <c r="O47" t="n">
-        <v>27.08513964838585</v>
+        <v>26.62399668881312</v>
       </c>
       <c r="P47" t="n">
-        <v>1.027133844897121</v>
+        <v>1.026672874456598</v>
       </c>
       <c r="Q47" t="n">
-        <v>1033595050.764206</v>
+        <v>282697279.5114288</v>
       </c>
       <c r="R47" t="n">
-        <v>58910.12280002013</v>
+        <v>4626.440395699151</v>
       </c>
       <c r="S47" t="n">
-        <v>0.005699536076189985</v>
+        <v>0.001636535167121095</v>
       </c>
       <c r="T47" t="n">
-        <v>106.1640458558074</v>
+        <v>29.02376285570589</v>
       </c>
       <c r="U47" t="n">
-        <v>0.006050858093494624</v>
+        <v>0.0004749840859554567</v>
       </c>
     </row>
     <row r="48">
@@ -3753,7 +3747,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="D48" t="n">
         <v>72.60066666666667</v>
@@ -3768,46 +3762,46 @@
         <v>0.5347685185185185</v>
       </c>
       <c r="H48" t="n">
-        <v>264.825</v>
+        <v>238.694</v>
       </c>
       <c r="I48" t="n">
-        <v>261.9374893110559</v>
+        <v>236.1063197972578</v>
       </c>
       <c r="J48" t="n">
-        <v>-0.5711000000000001</v>
+        <v>-1.0558</v>
       </c>
       <c r="K48" t="n">
-        <v>-0.5757446318269328</v>
+        <v>-1.056958930295232</v>
       </c>
       <c r="L48" t="n">
-        <v>-0.5793466493518202</v>
+        <v>-1.06189709177131</v>
       </c>
       <c r="M48" t="n">
-        <v>34.1762</v>
+        <v>33.672</v>
       </c>
       <c r="N48" t="n">
-        <v>34.34156513118191</v>
+        <v>33.83515912793373</v>
       </c>
       <c r="O48" t="n">
-        <v>27.47368530170365</v>
+        <v>27.08513964838585</v>
       </c>
       <c r="P48" t="n">
-        <v>1.027522191846997</v>
+        <v>1.027133844897121</v>
       </c>
       <c r="Q48" t="n">
-        <v>1866214059.550586</v>
+        <v>1033595050.764206</v>
       </c>
       <c r="R48" t="n">
-        <v>200028.3087420697</v>
+        <v>58910.12280002013</v>
       </c>
       <c r="S48" t="n">
-        <v>0.0107184011243726</v>
+        <v>0.005699536076189985</v>
       </c>
       <c r="T48" t="n">
-        <v>191.7576360925102</v>
+        <v>106.1640458558074</v>
       </c>
       <c r="U48" t="n">
-        <v>0.02055335262300994</v>
+        <v>0.006050858093494624</v>
       </c>
     </row>
     <row r="49">
@@ -3822,7 +3816,7 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>892</v>
+        <v>895</v>
       </c>
       <c r="D49" t="n">
         <v>72.60066666666667</v>
@@ -3837,46 +3831,46 @@
         <v>0.5347685185185185</v>
       </c>
       <c r="H49" t="n">
-        <v>360.561</v>
+        <v>264.825</v>
       </c>
       <c r="I49" t="n">
-        <v>356.5472121199587</v>
+        <v>261.9374893110559</v>
       </c>
       <c r="J49" t="n">
-        <v>0.4623</v>
+        <v>-0.5711000000000001</v>
       </c>
       <c r="K49" t="n">
-        <v>0.4478777357382848</v>
+        <v>-0.5757446318269328</v>
       </c>
       <c r="L49" t="n">
-        <v>0.4471133558146974</v>
+        <v>-0.5793466493518202</v>
       </c>
       <c r="M49" t="n">
-        <v>34.724</v>
+        <v>34.1762</v>
       </c>
       <c r="N49" t="n">
-        <v>34.89179925933443</v>
+        <v>34.34156513118191</v>
       </c>
       <c r="O49" t="n">
-        <v>27.86233839446322</v>
+        <v>27.47368530170365</v>
       </c>
       <c r="P49" t="n">
-        <v>1.027910479749956</v>
+        <v>1.027522191846997</v>
       </c>
       <c r="Q49" t="n">
-        <v>1708565700.356061</v>
+        <v>1866214059.550586</v>
       </c>
       <c r="R49" t="n">
-        <v>144742.3356718216</v>
+        <v>200028.3087420697</v>
       </c>
       <c r="S49" t="n">
-        <v>0.008471569787550906</v>
+        <v>0.0107184011243726</v>
       </c>
       <c r="T49" t="n">
-        <v>175.6252588737319</v>
+        <v>191.7576360925102</v>
       </c>
       <c r="U49" t="n">
-        <v>0.01487821637005514</v>
+        <v>0.02055335262300994</v>
       </c>
     </row>
     <row r="50">
@@ -3891,7 +3885,7 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>890</v>
+        <v>892</v>
       </c>
       <c r="D50" t="n">
         <v>72.60066666666667</v>
@@ -3906,46 +3900,46 @@
         <v>0.5347685185185185</v>
       </c>
       <c r="H50" t="n">
-        <v>486.153</v>
+        <v>360.561</v>
       </c>
       <c r="I50" t="n">
-        <v>480.59565519957</v>
+        <v>356.5472121199587</v>
       </c>
       <c r="J50" t="n">
-        <v>0.7563</v>
+        <v>0.4623</v>
       </c>
       <c r="K50" t="n">
-        <v>0.7338886913579263</v>
+        <v>0.4478777357382848</v>
       </c>
       <c r="L50" t="n">
-        <v>0.7339621137255654</v>
+        <v>0.4471133558146974</v>
       </c>
       <c r="M50" t="n">
-        <v>34.8285</v>
+        <v>34.724</v>
       </c>
       <c r="N50" t="n">
-        <v>34.99632796384559</v>
+        <v>34.89179925933443</v>
       </c>
       <c r="O50" t="n">
-        <v>27.92841168377481</v>
+        <v>27.86233839446322</v>
       </c>
       <c r="P50" t="n">
-        <v>1.027976457574439</v>
+        <v>1.027910479749956</v>
       </c>
       <c r="Q50" t="n">
-        <v>1380898447.594896</v>
+        <v>1708565700.356061</v>
       </c>
       <c r="R50" t="n">
-        <v>90302.09050298217</v>
+        <v>144742.3356718216</v>
       </c>
       <c r="S50" t="n">
-        <v>0.006539372294918635</v>
+        <v>0.008471569787550906</v>
       </c>
       <c r="T50" t="n">
-        <v>141.9531094428644</v>
+        <v>175.6252588737319</v>
       </c>
       <c r="U50" t="n">
-        <v>0.009282842310682202</v>
+        <v>0.01487821637005514</v>
       </c>
     </row>
     <row r="51">
@@ -3960,7 +3954,7 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="D51" t="n">
         <v>72.60066666666667</v>
@@ -3975,46 +3969,46 @@
         <v>0.5347685185185185</v>
       </c>
       <c r="H51" t="n">
-        <v>610.3579999999999</v>
+        <v>486.153</v>
       </c>
       <c r="I51" t="n">
-        <v>603.2006933858514</v>
+        <v>480.59565519957</v>
       </c>
       <c r="J51" t="n">
-        <v>0.6352</v>
+        <v>0.7563</v>
       </c>
       <c r="K51" t="n">
-        <v>0.6070387383626014</v>
+        <v>0.7338886913579263</v>
       </c>
       <c r="L51" t="n">
-        <v>0.6070866119318999</v>
+        <v>0.7339621137255654</v>
       </c>
       <c r="M51" t="n">
-        <v>34.8505</v>
+        <v>34.8285</v>
       </c>
       <c r="N51" t="n">
-        <v>35.01803196869508</v>
+        <v>34.99632796384559</v>
       </c>
       <c r="O51" t="n">
-        <v>27.95376662697481</v>
+        <v>27.92841168377481</v>
       </c>
       <c r="P51" t="n">
-        <v>1.028001848664071</v>
+        <v>1.027976457574439</v>
       </c>
       <c r="Q51" t="n">
-        <v>1550302454.019196</v>
+        <v>1380898447.594896</v>
       </c>
       <c r="R51" t="n">
-        <v>116014.1928216551</v>
+        <v>90302.09050298217</v>
       </c>
       <c r="S51" t="n">
-        <v>0.007483326400012172</v>
+        <v>0.006539372294918635</v>
       </c>
       <c r="T51" t="n">
-        <v>159.3713788720179</v>
+        <v>141.9531094428644</v>
       </c>
       <c r="U51" t="n">
-        <v>0.01192628046919313</v>
+        <v>0.009282842310682202</v>
       </c>
     </row>
     <row r="52">
@@ -4029,7 +4023,7 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="D52" t="n">
         <v>72.60066666666667</v>
@@ -4044,46 +4038,46 @@
         <v>0.5347685185185185</v>
       </c>
       <c r="H52" t="n">
-        <v>813.163</v>
+        <v>610.3579999999999</v>
       </c>
       <c r="I52" t="n">
-        <v>803.2369610664148</v>
+        <v>603.2006933858514</v>
       </c>
       <c r="J52" t="n">
-        <v>0.2983</v>
+        <v>0.6352</v>
       </c>
       <c r="K52" t="n">
-        <v>0.2619638193882665</v>
+        <v>0.6070387383626014</v>
       </c>
       <c r="L52" t="n">
-        <v>0.2616809449603927</v>
+        <v>0.6070866119318999</v>
       </c>
       <c r="M52" t="n">
-        <v>34.8635</v>
+        <v>34.8505</v>
       </c>
       <c r="N52" t="n">
-        <v>35.03092561652985</v>
+        <v>35.01803196869508</v>
       </c>
       <c r="O52" t="n">
-        <v>27.98474798142229</v>
+        <v>27.95376662697481</v>
       </c>
       <c r="P52" t="n">
-        <v>1.028032933278214</v>
+        <v>1.028001848664071</v>
       </c>
       <c r="Q52" t="n">
-        <v>1494754551.785483</v>
+        <v>1550302454.019196</v>
       </c>
       <c r="R52" t="n">
-        <v>123035.6791646019</v>
+        <v>116014.1928216551</v>
       </c>
       <c r="S52" t="n">
-        <v>0.008231162702775241</v>
+        <v>0.007483326400012172</v>
       </c>
       <c r="T52" t="n">
-        <v>153.6656906402993</v>
+        <v>159.3713788720179</v>
       </c>
       <c r="U52" t="n">
-        <v>0.0126484730149463</v>
+        <v>0.01192628046919313</v>
       </c>
     </row>
     <row r="53">
@@ -4098,7 +4092,7 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="D53" t="n">
         <v>72.60066666666667</v>
@@ -4113,46 +4107,46 @@
         <v>0.5347685185185185</v>
       </c>
       <c r="H53" t="n">
-        <v>1015.98</v>
+        <v>813.163</v>
       </c>
       <c r="I53" t="n">
-        <v>1003.092265578317</v>
+        <v>803.2369610664148</v>
       </c>
       <c r="J53" t="n">
-        <v>0.0605</v>
+        <v>0.2983</v>
       </c>
       <c r="K53" t="n">
-        <v>0.01545661202373176</v>
+        <v>0.2619638193882665</v>
       </c>
       <c r="L53" t="n">
-        <v>0.01493374212460613</v>
+        <v>0.2616809449603927</v>
       </c>
       <c r="M53" t="n">
-        <v>34.8738</v>
+        <v>34.8635</v>
       </c>
       <c r="N53" t="n">
-        <v>35.04128445703498</v>
+        <v>35.03092561652985</v>
       </c>
       <c r="O53" t="n">
-        <v>28.00684792419429</v>
+        <v>27.98474798142229</v>
       </c>
       <c r="P53" t="n">
-        <v>1.028055107616151</v>
+        <v>1.028032933278214</v>
       </c>
       <c r="Q53" t="n">
-        <v>1053503671.273536</v>
+        <v>1494754551.785483</v>
       </c>
       <c r="R53" t="n">
-        <v>58288.26164454089</v>
+        <v>123035.6791646019</v>
       </c>
       <c r="S53" t="n">
-        <v>0.005532800998602945</v>
+        <v>0.008231162702775241</v>
       </c>
       <c r="T53" t="n">
-        <v>108.3059830145126</v>
+        <v>153.6656906402993</v>
       </c>
       <c r="U53" t="n">
-        <v>0.005992354509773688</v>
+        <v>0.0126484730149463</v>
       </c>
     </row>
     <row r="54">
@@ -4167,7 +4161,7 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="D54" t="n">
         <v>72.60066666666667</v>
@@ -4182,46 +4176,46 @@
         <v>0.5347685185185185</v>
       </c>
       <c r="H54" t="n">
-        <v>1524.097</v>
+        <v>1015.98</v>
       </c>
       <c r="I54" t="n">
-        <v>1502.950676105728</v>
+        <v>1003.092265578317</v>
       </c>
       <c r="J54" t="n">
-        <v>-0.2938</v>
+        <v>0.0605</v>
       </c>
       <c r="K54" t="n">
-        <v>-0.363756641324205</v>
+        <v>0.01545661202373176</v>
       </c>
       <c r="L54" t="n">
-        <v>-0.3645992432288863</v>
+        <v>0.01493374212460613</v>
       </c>
       <c r="M54" t="n">
-        <v>34.9059</v>
+        <v>34.8738</v>
       </c>
       <c r="N54" t="n">
-        <v>35.07410419659686</v>
+        <v>35.04128445703498</v>
       </c>
       <c r="O54" t="n">
-        <v>28.05285341159151</v>
+        <v>28.00684792419429</v>
       </c>
       <c r="P54" t="n">
-        <v>1.028101227225429</v>
+        <v>1.028055107616151</v>
       </c>
       <c r="Q54" t="n">
-        <v>528249188.6842395</v>
+        <v>1053503671.273536</v>
       </c>
       <c r="R54" t="n">
-        <v>15651.41699837484</v>
+        <v>58288.26164454089</v>
       </c>
       <c r="S54" t="n">
-        <v>0.002962885193891034</v>
+        <v>0.005532800998602945</v>
       </c>
       <c r="T54" t="n">
-        <v>54.30936391671037</v>
+        <v>108.3059830145126</v>
       </c>
       <c r="U54" t="n">
-        <v>0.001609124102384611</v>
+        <v>0.005992354509773688</v>
       </c>
     </row>
     <row r="55">
@@ -4236,7 +4230,7 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="D55" t="n">
         <v>72.60066666666667</v>
@@ -4251,46 +4245,181 @@
         <v>0.5347685185185185</v>
       </c>
       <c r="H55" t="n">
+        <v>1524.097</v>
+      </c>
+      <c r="I55" t="n">
+        <v>1502.950676105728</v>
+      </c>
+      <c r="J55" t="n">
+        <v>-0.2938</v>
+      </c>
+      <c r="K55" t="n">
+        <v>-0.363756641324205</v>
+      </c>
+      <c r="L55" t="n">
+        <v>-0.3645992432288863</v>
+      </c>
+      <c r="M55" t="n">
+        <v>34.9059</v>
+      </c>
+      <c r="N55" t="n">
+        <v>35.07410419659686</v>
+      </c>
+      <c r="O55" t="n">
+        <v>28.05285341159151</v>
+      </c>
+      <c r="P55" t="n">
+        <v>1.028101227225429</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>528249188.6842395</v>
+      </c>
+      <c r="R55" t="n">
+        <v>15651.41699837484</v>
+      </c>
+      <c r="S55" t="n">
+        <v>0.002962885193891034</v>
+      </c>
+      <c r="T55" t="n">
+        <v>54.30936391671037</v>
+      </c>
+      <c r="U55" t="n">
+        <v>0.001609124102384611</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>JOIS 2024</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Stn A</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>884</v>
+      </c>
+      <c r="D56" t="n">
+        <v>72.60066666666667</v>
+      </c>
+      <c r="E56" t="n">
+        <v>-144.697</v>
+      </c>
+      <c r="F56" s="1" t="n">
+        <v>45553</v>
+      </c>
+      <c r="G56" s="2" t="n">
+        <v>0.5347685185185185</v>
+      </c>
+      <c r="H56" t="n">
         <v>2033.672</v>
       </c>
-      <c r="I55" t="n">
+      <c r="I56" t="n">
         <v>2003.054457465972</v>
       </c>
-      <c r="J55" t="n">
+      <c r="J56" t="n">
         <v>-0.3998</v>
       </c>
-      <c r="K55" t="n">
+      <c r="K56" t="n">
         <v>-0.5007895842021001</v>
       </c>
-      <c r="L55" t="n">
+      <c r="L56" t="n">
         <v>-0.5016867899119921</v>
       </c>
-      <c r="M55" t="n">
+      <c r="M56" t="n">
         <v>34.9366</v>
       </c>
-      <c r="N55" t="n">
+      <c r="N56" t="n">
         <v>35.10526799402068</v>
       </c>
-      <c r="O55" t="n">
+      <c r="O56" t="n">
         <v>28.08454343257631</v>
       </c>
-      <c r="P55" t="n">
+      <c r="P56" t="n">
         <v>1.028132957091159</v>
       </c>
-      <c r="Q55" t="n">
+      <c r="Q56" t="n">
         <v>66499053.13537027</v>
       </c>
-      <c r="R55" t="n">
+      <c r="R56" t="n">
         <v>290.5085146149778</v>
       </c>
-      <c r="S55" t="n">
+      <c r="S56" t="n">
         <v>0.0004368611294714192</v>
       </c>
-      <c r="T55" t="n">
+      <c r="T56" t="n">
         <v>6.836986814383036</v>
       </c>
-      <c r="U55" t="n">
+      <c r="U56" t="n">
         <v>2.986813781912574e-05</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>JOIS 2024</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Stn A</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>882</v>
+      </c>
+      <c r="D57" t="n">
+        <v>72.60066666666667</v>
+      </c>
+      <c r="E57" t="n">
+        <v>-144.697</v>
+      </c>
+      <c r="F57" s="1" t="n">
+        <v>45553</v>
+      </c>
+      <c r="G57" s="2" t="n">
+        <v>0.5347685185185185</v>
+      </c>
+      <c r="H57" t="n">
+        <v>3392.083</v>
+      </c>
+      <c r="I57" t="n">
+        <v>3330.540309141927</v>
+      </c>
+      <c r="J57" t="n">
+        <v>-0.2924</v>
+      </c>
+      <c r="K57" t="n">
+        <v>-0.5031551907890527</v>
+      </c>
+      <c r="L57" t="n">
+        <v>-0.5039922538192495</v>
+      </c>
+      <c r="M57" t="n">
+        <v>34.9533</v>
+      </c>
+      <c r="N57" t="n">
+        <v>35.12270525899957</v>
+      </c>
+      <c r="O57" t="n">
+        <v>28.09868008599119</v>
+      </c>
+      <c r="P57" t="n">
+        <v>1.028147092899139</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>0</v>
+      </c>
+      <c r="R57" t="n">
+        <v>0</v>
+      </c>
+      <c r="T57" t="n">
+        <v>0</v>
+      </c>
+      <c r="U57" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
